--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,12 +662,101 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-14 09:46:51</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1531.8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1520</v>
+      </c>
+      <c r="I3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="K3" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="L3" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="M3" t="n">
+        <v>47.78</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1760</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="S3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>55.08</v>
+      </c>
+      <c r="U3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>NSE:MFSL26AUG1520PE</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -751,12 +751,11 @@
           <t>NSE:MFSL26AUG1520PE</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-14 09:49:03</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -751,11 +751,7 @@
           <t>NSE:MFSL26AUG1520PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-14 09:49:03</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -751,7 +751,11 @@
           <t>NSE:MFSL26AUG1520PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:04:50</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:07:01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -749,11 +754,6 @@
       <c r="W3" t="inlineStr">
         <is>
           <t>NSE:MFSL26AUG1520PE</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-14 10:04:50</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -756,6 +756,11 @@
           <t>NSE:MFSL26AUG1520PE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:09:25</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,11 +662,7 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-08-14 10:07:01</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,7 +662,11 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:14:24</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -755,6 +759,95 @@
       <c r="AC3" t="inlineStr">
         <is>
           <t>2026-08-14 10:09:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:14:23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-5.64</v>
+      </c>
+      <c r="H4" t="n">
+        <v>330</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7462</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="S4" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="U4" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NSE:TMPV26AUG330PE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -850,6 +850,101 @@
           <t>NSE:TMPV26AUG330PE</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3385</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3400</v>
+      </c>
+      <c r="I5" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="K5" t="n">
+        <v>70.06</v>
+      </c>
+      <c r="L5" t="n">
+        <v>81.68000000000001</v>
+      </c>
+      <c r="M5" t="n">
+        <v>97.18000000000001</v>
+      </c>
+      <c r="N5" t="n">
+        <v>986</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="S5" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="U5" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NSE:M&amp;M26AUG3400CE</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -756,11 +756,6 @@
           <t>NSE:MFSL26AUG1520PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-14 10:09:25</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -939,12 +934,11 @@
           <t>NSE:M&amp;M26AUG3400CE</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:21:41</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,11 +662,7 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-08-14 10:14:24</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,7 +662,6 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -752,6 +751,11 @@
           <t>NSE:MFSL26AUG1520PE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:31:45</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -839,6 +843,11 @@
       <c r="W4" t="inlineStr">
         <is>
           <t>NSE:TMPV26AUG330PE</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:31:45</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -751,11 +751,7 @@
           <t>NSE:MFSL26AUG1520PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-14 10:31:45</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,6 +662,11 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:49:15</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -751,7 +756,6 @@
           <t>NSE:MFSL26AUG1520PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -938,6 +942,95 @@
       <c r="AC5" t="inlineStr">
         <is>
           <t>2026-08-14 10:21:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:49:15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1970.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1980</v>
+      </c>
+      <c r="I6" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="K6" t="n">
+        <v>31.31</v>
+      </c>
+      <c r="L6" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="M6" t="n">
+        <v>43.86</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2237</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="S6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>63.97</v>
+      </c>
+      <c r="U6" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NSE:BHARTIARTL26AUG1980CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -845,11 +845,7 @@
           <t>NSE:TMPV26AUG330PE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-08-14 10:31:45</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -756,6 +756,11 @@
           <t>NSE:MFSL26AUG1520PE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:56:41</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -845,7 +850,6 @@
           <t>NSE:TMPV26AUG330PE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1027,6 +1031,11 @@
       <c r="W6" t="inlineStr">
         <is>
           <t>NSE:BHARTIARTL26AUG1980CE</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:56:41</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,11 +662,6 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-08-14 10:49:15</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -848,6 +843,11 @@
       <c r="W4" t="inlineStr">
         <is>
           <t>NSE:TMPV26AUG330PE</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:58:50</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:00:59</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,6 +1043,101 @@
           <t>2026-08-14 10:56:41</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:05:14</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3446.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3400</v>
+      </c>
+      <c r="I7" t="n">
+        <v>67.05</v>
+      </c>
+      <c r="J7" t="n">
+        <v>44</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.63</v>
+      </c>
+      <c r="L7" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="M7" t="n">
+        <v>116.44</v>
+      </c>
+      <c r="N7" t="n">
+        <v>745</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="S7" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="U7" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:BSE26AUG3400PE</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -1038,6 +1038,16 @@
           <t>NSE:BHARTIARTL26AUG1980CE</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:06:09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>2026-08-14 10:56:41</t>
@@ -1132,12 +1142,6 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,11 +662,7 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-08-14 11:00:59</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,7 +662,6 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -846,11 +845,7 @@
           <t>NSE:TMPV26AUG330PE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-08-14 10:58:50</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:11:45</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -845,7 +850,11 @@
           <t>NSE:TMPV26AUG330PE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:11:45</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -850,11 +850,7 @@
           <t>NSE:TMPV26AUG330PE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-08-14 11:11:45</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -756,11 +756,6 @@
           <t>NSE:MFSL26AUG1520PE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-14 10:56:41</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -850,7 +845,6 @@
           <t>NSE:TMPV26AUG330PE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1136,6 +1130,11 @@
       <c r="W7" t="inlineStr">
         <is>
           <t>NSE:BSE26AUG3400PE</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:20:27</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -756,6 +756,16 @@
           <t>NSE:MFSL26AUG1520PE</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:22:38</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1130,11 +1140,6 @@
       <c r="W7" t="inlineStr">
         <is>
           <t>NSE:BSE26AUG3400PE</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-08-14 11:20:27</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -1142,6 +1142,11 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:24:45</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -766,6 +766,11 @@
           <t>SL Hit</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:31:11</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -766,11 +766,7 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-14 11:31:11</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,11 +662,7 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-08-14 11:11:45</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -766,7 +762,6 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,7 +662,11 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:37:39</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,11 +662,7 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-08-14 11:37:39</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,7 +662,11 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:41:57</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1136,11 +1140,6 @@
       <c r="W7" t="inlineStr">
         <is>
           <t>NSE:BSE26AUG3400PE</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-08-14 11:24:45</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,11 +662,6 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-08-14 11:41:57</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1140,6 +1135,11 @@
       <c r="W7" t="inlineStr">
         <is>
           <t>NSE:BSE26AUG3400PE</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:44:10</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -1038,9 +1038,14 @@
           <t>2026-08-14 11:06:09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:46:27</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:50:43</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,11 +662,7 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-08-14 11:50:43</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,7 +662,6 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1143,11 +1142,7 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-08-14 11:44:10</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -1142,7 +1142,11 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-14 12:08:25</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -1142,11 +1142,7 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-08-14 12:08:25</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-14 12:12:49</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1142,7 +1147,6 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,279 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-14 12:18:02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3446.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3400</v>
+      </c>
+      <c r="I8" t="n">
+        <v>66.55</v>
+      </c>
+      <c r="J8" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.37</v>
+      </c>
+      <c r="L8" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="M8" t="n">
+        <v>116.53</v>
+      </c>
+      <c r="N8" t="n">
+        <v>751</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S8" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>44.95</v>
+      </c>
+      <c r="U8" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:BSE26AUG3400PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14 12:18:02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>332.45</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-4.91</v>
+      </c>
+      <c r="H9" t="n">
+        <v>330</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9900</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="S9" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="U9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:TMPV26AUG330PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-14 12:18:02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1547.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1540</v>
+      </c>
+      <c r="I10" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="K10" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="L10" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="M10" t="n">
+        <v>44.87</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1976</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="S10" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>58.52</v>
+      </c>
+      <c r="U10" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:MFSL26AUG1540PE</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,12 +1414,279 @@
           <t>NSE:MFSL26AUG1540PE</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-14 12:19:29</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3443.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3400</v>
+      </c>
+      <c r="I11" t="n">
+        <v>66.55</v>
+      </c>
+      <c r="J11" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.37</v>
+      </c>
+      <c r="L11" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="M11" t="n">
+        <v>116.53</v>
+      </c>
+      <c r="N11" t="n">
+        <v>751</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S11" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>44.95</v>
+      </c>
+      <c r="U11" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:BSE26AUG3400PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-14 12:19:29</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>332.45</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-4.91</v>
+      </c>
+      <c r="H12" t="n">
+        <v>330</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="S12" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="U12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NSE:TMPV26AUG330PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-14 12:19:29</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1554</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1560</v>
+      </c>
+      <c r="I13" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="K13" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="L13" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="M13" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1567</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="S13" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>59.87</v>
+      </c>
+      <c r="U13" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NSE:MFSL26AUG1560PE</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -1503,6 +1503,11 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-08-14 12:21:47</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1681,12 +1686,6 @@
           <t>NSE:MFSL26AUG1560PE</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -1503,11 +1503,7 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2026-08-14 12:21:47</t>
-        </is>
-      </c>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -1503,7 +1503,11 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-08-14 12:52:47</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -1503,11 +1503,7 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2026-08-14 12:52:47</t>
-        </is>
-      </c>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -1503,7 +1503,11 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:19:17</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -1503,11 +1503,7 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2026-08-14 13:19:17</t>
-        </is>
-      </c>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1503,7 +1503,11 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-08-14 14:15:52</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1593,6 +1597,11 @@
           <t>NSE:TMPV26AUG330PE</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:13:29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1680,6 +1689,100 @@
       <c r="W13" t="inlineStr">
         <is>
           <t>NSE:MFSL26AUG1560PE</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:31:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-14 14:40:18</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1997.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I14" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="J14" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="K14" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="L14" t="n">
+        <v>39.31</v>
+      </c>
+      <c r="M14" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2188</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="S14" t="n">
+        <v>17</v>
+      </c>
+      <c r="T14" t="n">
+        <v>67.52</v>
+      </c>
+      <c r="U14" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>NSE:BHARTIARTL26AUG2000CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -662,6 +662,16 @@
           <t>NSE:PATANJALI26AUG350PE</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2026-08-14 14:42:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>2026-08-14 12:12:49</t>
@@ -853,6 +863,16 @@
       <c r="W4" t="inlineStr">
         <is>
           <t>NSE:TMPV26AUG330PE</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:11:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
+++ b/backend/signal_logs/2026-08-14/signals_2026-08-14.xlsx
@@ -964,6 +964,11 @@
           <t>NSE:M&amp;M26AUG3400CE</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Closed up ~51.0 (+0.6% from entry)</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>2026-08-14 10:21:41</t>
@@ -1167,6 +1172,11 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Closed down ~62.1 (-7.4% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1256,6 +1266,11 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Closed down ~62.1 (-6.7% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1345,6 +1360,11 @@
           <t>NSE:TMPV26AUG330PE</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Closed down ~4.4 (-12.9% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1434,6 +1454,11 @@
           <t>NSE:MFSL26AUG1540PE</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Closed down ~24.75 (-2.2% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1523,6 +1548,11 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Closed down ~64.1 (-3.7% from entry)</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>2026-08-14 14:15:52</t>
@@ -1617,6 +1647,11 @@
           <t>NSE:TMPV26AUG330PE</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Closed down ~4.1 (-18.0% from entry)</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>2026-08-14 15:13:29</t>
@@ -1711,6 +1746,11 @@
           <t>NSE:MFSL26AUG1560PE</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Closed up ~35.6 (+11.6% from entry)</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>2026-08-14 15:31:53</t>
@@ -1803,6 +1843,11 @@
       <c r="W14" t="inlineStr">
         <is>
           <t>NSE:BHARTIARTL26AUG2000CE</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Closed down ~18.0 (-21.2% from entry, EOD estimate)</t>
         </is>
       </c>
     </row>
